--- a/04_試験/結合テスト/052-バグ管理票.xlsx
+++ b/04_試験/結合テスト/052-バグ管理票.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\04_試験\結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF826B6D-D9E9-4907-83B7-A898B7B2F22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BE0840-9931-4032-A827-C44BF11D7CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題点一覧" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="259">
   <si>
     <t>状態</t>
     <rPh sb="0" eb="2">
@@ -3287,38 +3287,11 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>クラス仕様書に明確な記述がなかった</t>
-    <rPh sb="3" eb="6">
-      <t>シヨウショ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>メイカク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>キジュツ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>B-001</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
     <t>・検索結果が1ページ分しか存在しないとき、「前へ」、「1」、「次へ」が表示されない。</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>・実装されてないため</t>
-    <rPh sb="1" eb="3">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>・JSPにソースを追加する</t>
-    <rPh sb="9" eb="11">
-      <t>ツイカ</t>
-    </rPh>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -3366,6 +3339,119 @@
   </si>
   <si>
     <t>ecsite</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>B-002</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>・検索キーワード入力欄に、要件定義・外部設計・内部設計で定義されていない機能が存在した。
+・「キーワードを入力してください」というプレースホルダーが存在した。</t>
+    <rPh sb="36" eb="38">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>・実装されてないため。</t>
+    <rPh sb="1" eb="3">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>・JSPにソースを追加する。</t>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>・JSPからソースを削除する。</t>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>・コーディングの際、内部設計書の確認が疎かだったため。</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>・存在しないはずの機能が実装されていたため。</t>
+    <rPh sb="1" eb="3">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>クラス仕様書に明確な記述がなかったため。</t>
+    <rPh sb="3" eb="6">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キジュツ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>・コーディングの際は、内部設計書とのすり合わせを行うことを徹底する。
+・必要があれば、要件定義書や外部設計書も確認する。</t>
+    <rPh sb="8" eb="9">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="11" eb="16">
+      <t>ナイブセッケイショ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>テッテイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="43" eb="48">
+      <t>ヨウケンテイギショ</t>
+    </rPh>
+    <rPh sb="49" eb="54">
+      <t>ガイブセッケイショ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>結合試験
+02</t>
+    <rPh sb="0" eb="4">
+      <t>ケツゴウシケン</t>
+    </rPh>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -8380,7 +8466,7 @@
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="8" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D1" s="9"/>
     </row>
@@ -8442,36 +8528,38 @@
     </row>
     <row r="3" spans="1:18" ht="93.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E3" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F3" s="12">
         <v>45589</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>238</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="K3" s="12"/>
+        <v>245</v>
+      </c>
+      <c r="K3" s="12">
+        <v>45590</v>
+      </c>
       <c r="L3" s="25" t="s">
         <v>226</v>
       </c>
@@ -8488,31 +8576,67 @@
         <v>230</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="11"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F4" s="12">
+        <v>45590</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K4" s="12">
+        <v>45593</v>
+      </c>
+      <c r="L4" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="11"/>
@@ -11589,7 +11713,7 @@
         <v>72</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="22"/>
@@ -11634,7 +11758,7 @@
         <v>45589</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G3" s="8"/>
     </row>
